--- a/samples/사전과제_엑셀예시.xlsx
+++ b/samples/사전과제_엑셀예시.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -619,12 +619,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>부서</t>
+          <t>담당자</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>그 활동을 하는 조직. 순서도에서 가로 레인이 됩니다. 인사팀이 아닌 현업·입사자·타 부서도 그대로 적습니다.</t>
+          <t>그 활동을 하는 사람·역할. 순서도에서 가로 레인이 됩니다. 인사팀 담당자만 적지 말고 현업·입사자·타 부서·역할도 그대로 적습니다.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>시스템/도구</t>
+          <t>시스템/프로그램</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -655,34 +655,46 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>다음 단계</t>
+          <t>Input / Output</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>비워 두면 다음 행으로 이어집니다. 되돌아가거나 건너뛸 때만 순번이나 '종료'를 적습니다. 판단 행은 '조건→순번'을 쉼표로 구분. 예) 승인→3, 반려→종료</t>
+          <t>그 활동에 들어가는 자료와 나오는 결과물. 예) Input 입사 서류 → Output 인사정보 등록 완료</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t>다음 단계</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>문제점, 대기 시간, 예외 상황. 교육 당일 진단에 활용합니다.</t>
+          <t>비워 두면 다음 행으로 이어집니다. 되돌아가거나 건너뛸 때만 순번이나 '종료'를 적습니다. 판단 행은 '조건→순번'을 쉼표로 구분. 예) 승인→3, 반려→종료</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>문제점, 대기 시간, 예외 상황. 교육 당일 진단에 활용합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>제출</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>엑셀 파일이 아니라, 툴에서 [💾 저장]으로 만든 .json 파일을 제출합니다.</t>
         </is>
@@ -699,17 +711,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -945,30 +958,35 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>부서</t>
+          <t>담당자</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>담당자</t>
+          <t>활동명</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>활동명</t>
+          <t>시스템/프로그램</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>시스템/도구</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
           <t>다음 단계</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -985,26 +1003,23 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
           <t>채용담당</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>입사 확정 통보</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>메일, 전화</t>
         </is>
       </c>
+      <c r="F20" s="13" t="inlineStr"/>
       <c r="G20" s="13" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
@@ -1017,26 +1032,23 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
           <t>입사담당</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>입사 서류 안내</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>메일</t>
         </is>
       </c>
+      <c r="F21" s="13" t="inlineStr"/>
       <c r="G21" s="13" t="inlineStr"/>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr"/>
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>제출 서류 목록을 매번 메일로 새로 작성</t>
         </is>
@@ -1056,19 +1068,20 @@
           <t>입사자</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr"/>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>입사 서류 제출</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>메일, 종이/출력</t>
         </is>
       </c>
+      <c r="F22" s="13" t="inlineStr"/>
       <c r="G22" s="13" t="inlineStr"/>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>원본 서류는 첫 출근일에 지참</t>
         </is>
@@ -1085,30 +1098,27 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
           <t>입사담당</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>입사 서류 보완 필요 여부 판단</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>엑셀</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr"/>
+      <c r="G23" s="16" t="inlineStr"/>
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>보완 필요→5, 이상 없음→6</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>누락 여부를 엑셀 체크리스트로 확인</t>
         </is>
@@ -1128,23 +1138,24 @@
           <t>입사자</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>입사 서류 보완 제출</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>메일</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr"/>
+      <c r="G24" s="13" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
@@ -1157,26 +1168,23 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
           <t>입사담당</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>인사정보 등록</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>HRIS, 엑셀</t>
         </is>
       </c>
+      <c r="F25" s="13" t="inlineStr"/>
       <c r="G25" s="13" t="inlineStr"/>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>엑셀 입사자 대장과 HRIS에 이중 입력</t>
         </is>
@@ -1193,26 +1201,23 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
           <t>입사담당</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>IT 계정 생성 요청</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>메일</t>
         </is>
       </c>
+      <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
@@ -1225,26 +1230,23 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
           <t>시스템 담당</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>사내 계정·메일 생성</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>그룹웨어</t>
         </is>
       </c>
+      <c r="F27" s="13" t="inlineStr"/>
       <c r="G27" s="13" t="inlineStr"/>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr">
         <is>
           <t>요청이 누락되면 첫 출근일에 계정 없음</t>
         </is>
@@ -1261,26 +1263,23 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
           <t>입사담당</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>좌석·PC 준비 요청</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>메일, 메신저</t>
         </is>
       </c>
+      <c r="F28" s="13" t="inlineStr"/>
       <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n">
@@ -1293,26 +1292,23 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>총무</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
           <t>자산 담당</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>좌석·PC 배정</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>엑셀</t>
         </is>
       </c>
+      <c r="F29" s="13" t="inlineStr"/>
       <c r="G29" s="13" t="inlineStr"/>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H29" s="13" t="inlineStr"/>
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>장비 재고를 엑셀로 관리해 확인에 1~2일 소요</t>
         </is>
@@ -1329,26 +1325,23 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
           <t>급여담당</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>급여 계좌·4대보험 등록</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>HRIS, EDI</t>
         </is>
       </c>
+      <c r="F30" s="13" t="inlineStr"/>
       <c r="G30" s="13" t="inlineStr"/>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr"/>
+      <c r="I30" s="13" t="inlineStr">
         <is>
           <t>4대보험 취득신고 기한(입사 후 14일) 관리 필요</t>
         </is>
@@ -1365,26 +1358,23 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>현업 부서</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
           <t>팀장</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>멘토·첫 주 업무 지정</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>메일</t>
         </is>
       </c>
+      <c r="F31" s="13" t="inlineStr"/>
       <c r="G31" s="13" t="inlineStr"/>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr"/>
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>팀마다 준비 수준 편차가 큼</t>
         </is>
@@ -1401,26 +1391,23 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
           <t>입사담당</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>입사 오리엔테이션 진행</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>대면, 종이/출력</t>
         </is>
       </c>
+      <c r="F32" s="13" t="inlineStr"/>
       <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="13" t="inlineStr"/>
+      <c r="I32" s="13" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
@@ -1436,19 +1423,20 @@
           <t>입사자</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr"/>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>보안 서약서 서명</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>종이/출력</t>
         </is>
       </c>
+      <c r="F33" s="13" t="inlineStr"/>
       <c r="G33" s="13" t="inlineStr"/>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr"/>
+      <c r="I33" s="13" t="inlineStr">
         <is>
           <t>종이에 서명한 뒤 스캔해 보관</t>
         </is>
@@ -1463,13 +1451,13 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="A14:B14"/>
@@ -1497,17 +1485,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1743,30 +1732,35 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>부서</t>
+          <t>담당자</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>담당자</t>
+          <t>활동명</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>활동명</t>
+          <t>시스템/프로그램</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>시스템/도구</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
           <t>다음 단계</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1783,26 +1777,23 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>평가 일정·기준 수립</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>엑셀, 워드</t>
         </is>
       </c>
+      <c r="F20" s="13" t="inlineStr"/>
       <c r="G20" s="13" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
@@ -1815,30 +1806,27 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>경영진</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
           <t>인사 임원</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>평가 계획 승인 여부 판단</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>전자결재</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr"/>
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>승인→3, 보완 요청→1</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr"/>
+      <c r="I21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
@@ -1851,26 +1839,23 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>평가 대상자 명단 추출</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>HRIS, 엑셀</t>
         </is>
       </c>
+      <c r="F22" s="13" t="inlineStr"/>
       <c r="G22" s="13" t="inlineStr"/>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>휴직자·전입자는 수기로 보정</t>
         </is>
@@ -1887,26 +1872,23 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>평가 안내 공지</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>메일, 그룹웨어</t>
         </is>
       </c>
+      <c r="F23" s="13" t="inlineStr"/>
       <c r="G23" s="13" t="inlineStr"/>
       <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
@@ -1922,19 +1904,20 @@
           <t>임직원</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>자기평가 작성</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>HRIS</t>
         </is>
       </c>
+      <c r="F24" s="13" t="inlineStr"/>
       <c r="G24" s="13" t="inlineStr"/>
       <c r="H24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
@@ -1947,26 +1930,23 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>미제출자 독촉</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>메일, 전화, 메신저</t>
         </is>
       </c>
+      <c r="F25" s="13" t="inlineStr"/>
       <c r="G25" s="13" t="inlineStr"/>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>제출률을 엑셀로 집계해 개별 연락 (마감 전후 1주)</t>
         </is>
@@ -1983,26 +1963,23 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>현업 부서</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
           <t>1차 평가자(팀장)</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>1차 평가 입력</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>HRIS</t>
         </is>
       </c>
+      <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
@@ -2015,26 +1992,23 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>현업 부서</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
           <t>2차 평가자(본부장)</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>2차 평가 입력</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>HRIS</t>
         </is>
       </c>
+      <c r="F27" s="13" t="inlineStr"/>
       <c r="G27" s="13" t="inlineStr"/>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr">
         <is>
           <t>본부장 일정 때문에 지연이 잦음</t>
         </is>
@@ -2051,26 +2025,23 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>평가 등급 분포 검토</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>HRIS, 엑셀</t>
         </is>
       </c>
+      <c r="F28" s="13" t="inlineStr"/>
       <c r="G28" s="13" t="inlineStr"/>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>HRIS에서 내려받아 엑셀로 등급 비율 계산</t>
         </is>
@@ -2087,26 +2058,23 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>등급 분포 조정 필요 여부 판단</t>
         </is>
       </c>
+      <c r="E29" s="16" t="inlineStr"/>
       <c r="F29" s="16" t="inlineStr"/>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G29" s="16" t="inlineStr"/>
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>조정 필요→11, 이상 없음→12</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr"/>
+      <c r="I29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n">
@@ -2119,30 +2087,27 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>현업 부서</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
           <t>2차 평가자(본부장)</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>평가 등급 조정</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>HRIS, 메일</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr"/>
+      <c r="G30" s="13" t="inlineStr"/>
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr"/>
+      <c r="I30" s="13" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
@@ -2155,26 +2120,23 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>경영진</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
           <t>인사위원회</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>평가 결과 확정</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>대면, 종이/출력</t>
         </is>
       </c>
+      <c r="F31" s="13" t="inlineStr"/>
       <c r="G31" s="13" t="inlineStr"/>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr"/>
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>회의 자료 출력물 준비에 2~3일</t>
         </is>
@@ -2191,26 +2153,23 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>평가 결과 통보</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>HRIS, 메일</t>
         </is>
       </c>
+      <c r="F32" s="13" t="inlineStr"/>
       <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="13" t="inlineStr"/>
+      <c r="I32" s="13" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
@@ -2223,26 +2182,23 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>현업 부서</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
           <t>팀장</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>평가 피드백 면담</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>대면</t>
         </is>
       </c>
+      <c r="F33" s="13" t="inlineStr"/>
       <c r="G33" s="13" t="inlineStr"/>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr"/>
+      <c r="I33" s="13" t="inlineStr">
         <is>
           <t>면담 실시 여부를 확인할 방법이 없음</t>
         </is>
@@ -2262,19 +2218,20 @@
           <t>임직원</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr"/>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>이의 신청 여부 판단</t>
         </is>
       </c>
+      <c r="E34" s="16" t="inlineStr"/>
       <c r="F34" s="16" t="inlineStr"/>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G34" s="16" t="inlineStr"/>
+      <c r="H34" s="16" t="inlineStr">
         <is>
           <t>이의 신청→16, 없음→종료</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr"/>
+      <c r="I34" s="16" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="n">
@@ -2287,26 +2244,23 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>인사팀</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>이의 신청 검토·회신</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>메일, 엑셀</t>
         </is>
       </c>
+      <c r="F35" s="13" t="inlineStr"/>
       <c r="G35" s="13" t="inlineStr"/>
       <c r="H35" s="13" t="inlineStr"/>
+      <c r="I35" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -2317,13 +2271,13 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="A14:B14"/>
@@ -2351,17 +2305,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2549,30 +2504,35 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>부서</t>
+          <t>담당자</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>담당자</t>
+          <t>활동명</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>활동명</t>
+          <t>시스템/프로그램</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>시스템/도구</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
           <t>다음 단계</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2588,11 +2548,12 @@
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr"/>
-      <c r="D20" s="13" t="inlineStr"/>
-      <c r="E20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr"/>
+      <c r="E20" s="13" t="inlineStr"/>
       <c r="F20" s="13" t="inlineStr"/>
       <c r="G20" s="13" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
@@ -2604,11 +2565,12 @@
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr"/>
-      <c r="D21" s="13" t="inlineStr"/>
-      <c r="E21" s="14" t="inlineStr"/>
+      <c r="D21" s="14" t="inlineStr"/>
+      <c r="E21" s="13" t="inlineStr"/>
       <c r="F21" s="13" t="inlineStr"/>
       <c r="G21" s="13" t="inlineStr"/>
       <c r="H21" s="13" t="inlineStr"/>
+      <c r="I21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
@@ -2620,11 +2582,12 @@
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr"/>
-      <c r="D22" s="13" t="inlineStr"/>
-      <c r="E22" s="14" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr"/>
+      <c r="E22" s="13" t="inlineStr"/>
       <c r="F22" s="13" t="inlineStr"/>
       <c r="G22" s="13" t="inlineStr"/>
       <c r="H22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
@@ -2636,11 +2599,12 @@
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr"/>
-      <c r="D23" s="13" t="inlineStr"/>
-      <c r="E23" s="14" t="inlineStr"/>
+      <c r="D23" s="14" t="inlineStr"/>
+      <c r="E23" s="13" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr"/>
       <c r="G23" s="13" t="inlineStr"/>
       <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
@@ -2652,11 +2616,12 @@
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr"/>
-      <c r="D24" s="13" t="inlineStr"/>
-      <c r="E24" s="14" t="inlineStr"/>
+      <c r="D24" s="14" t="inlineStr"/>
+      <c r="E24" s="13" t="inlineStr"/>
       <c r="F24" s="13" t="inlineStr"/>
       <c r="G24" s="13" t="inlineStr"/>
       <c r="H24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
@@ -2668,11 +2633,12 @@
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr"/>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="14" t="inlineStr"/>
+      <c r="D25" s="14" t="inlineStr"/>
+      <c r="E25" s="13" t="inlineStr"/>
       <c r="F25" s="13" t="inlineStr"/>
       <c r="G25" s="13" t="inlineStr"/>
       <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
@@ -2684,11 +2650,12 @@
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr"/>
-      <c r="D26" s="13" t="inlineStr"/>
-      <c r="E26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="13" t="inlineStr"/>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
@@ -2700,11 +2667,12 @@
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr"/>
-      <c r="D27" s="13" t="inlineStr"/>
-      <c r="E27" s="14" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr"/>
+      <c r="E27" s="13" t="inlineStr"/>
       <c r="F27" s="13" t="inlineStr"/>
       <c r="G27" s="13" t="inlineStr"/>
       <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
@@ -2716,11 +2684,12 @@
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr"/>
-      <c r="D28" s="13" t="inlineStr"/>
-      <c r="E28" s="14" t="inlineStr"/>
+      <c r="D28" s="14" t="inlineStr"/>
+      <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="13" t="inlineStr"/>
       <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n">
@@ -2732,11 +2701,12 @@
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr"/>
-      <c r="D29" s="13" t="inlineStr"/>
-      <c r="E29" s="14" t="inlineStr"/>
+      <c r="D29" s="14" t="inlineStr"/>
+      <c r="E29" s="13" t="inlineStr"/>
       <c r="F29" s="13" t="inlineStr"/>
       <c r="G29" s="13" t="inlineStr"/>
       <c r="H29" s="13" t="inlineStr"/>
+      <c r="I29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n">
@@ -2748,11 +2718,12 @@
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr"/>
-      <c r="D30" s="13" t="inlineStr"/>
-      <c r="E30" s="14" t="inlineStr"/>
+      <c r="D30" s="14" t="inlineStr"/>
+      <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="13" t="inlineStr"/>
       <c r="G30" s="13" t="inlineStr"/>
       <c r="H30" s="13" t="inlineStr"/>
+      <c r="I30" s="13" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
@@ -2764,11 +2735,12 @@
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr"/>
-      <c r="D31" s="13" t="inlineStr"/>
-      <c r="E31" s="14" t="inlineStr"/>
+      <c r="D31" s="14" t="inlineStr"/>
+      <c r="E31" s="13" t="inlineStr"/>
       <c r="F31" s="13" t="inlineStr"/>
       <c r="G31" s="13" t="inlineStr"/>
       <c r="H31" s="13" t="inlineStr"/>
+      <c r="I31" s="13" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
@@ -2780,11 +2752,12 @@
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr"/>
-      <c r="D32" s="13" t="inlineStr"/>
-      <c r="E32" s="14" t="inlineStr"/>
+      <c r="D32" s="14" t="inlineStr"/>
+      <c r="E32" s="13" t="inlineStr"/>
       <c r="F32" s="13" t="inlineStr"/>
       <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="13" t="inlineStr"/>
+      <c r="I32" s="13" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
@@ -2796,11 +2769,12 @@
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr"/>
-      <c r="D33" s="13" t="inlineStr"/>
-      <c r="E33" s="14" t="inlineStr"/>
+      <c r="D33" s="14" t="inlineStr"/>
+      <c r="E33" s="13" t="inlineStr"/>
       <c r="F33" s="13" t="inlineStr"/>
       <c r="G33" s="13" t="inlineStr"/>
       <c r="H33" s="13" t="inlineStr"/>
+      <c r="I33" s="13" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n">
@@ -2812,11 +2786,12 @@
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr"/>
-      <c r="D34" s="13" t="inlineStr"/>
-      <c r="E34" s="14" t="inlineStr"/>
+      <c r="D34" s="14" t="inlineStr"/>
+      <c r="E34" s="13" t="inlineStr"/>
       <c r="F34" s="13" t="inlineStr"/>
       <c r="G34" s="13" t="inlineStr"/>
       <c r="H34" s="13" t="inlineStr"/>
+      <c r="I34" s="13" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="n">
@@ -2828,11 +2803,12 @@
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr"/>
-      <c r="D35" s="13" t="inlineStr"/>
-      <c r="E35" s="14" t="inlineStr"/>
+      <c r="D35" s="14" t="inlineStr"/>
+      <c r="E35" s="13" t="inlineStr"/>
       <c r="F35" s="13" t="inlineStr"/>
       <c r="G35" s="13" t="inlineStr"/>
       <c r="H35" s="13" t="inlineStr"/>
+      <c r="I35" s="13" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n">
@@ -2844,11 +2820,12 @@
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr"/>
-      <c r="D36" s="13" t="inlineStr"/>
-      <c r="E36" s="14" t="inlineStr"/>
+      <c r="D36" s="14" t="inlineStr"/>
+      <c r="E36" s="13" t="inlineStr"/>
       <c r="F36" s="13" t="inlineStr"/>
       <c r="G36" s="13" t="inlineStr"/>
       <c r="H36" s="13" t="inlineStr"/>
+      <c r="I36" s="13" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
@@ -2860,11 +2837,12 @@
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr"/>
-      <c r="D37" s="13" t="inlineStr"/>
-      <c r="E37" s="14" t="inlineStr"/>
+      <c r="D37" s="14" t="inlineStr"/>
+      <c r="E37" s="13" t="inlineStr"/>
       <c r="F37" s="13" t="inlineStr"/>
       <c r="G37" s="13" t="inlineStr"/>
       <c r="H37" s="13" t="inlineStr"/>
+      <c r="I37" s="13" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n">
@@ -2876,11 +2854,12 @@
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr"/>
-      <c r="D38" s="13" t="inlineStr"/>
-      <c r="E38" s="14" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr"/>
+      <c r="E38" s="13" t="inlineStr"/>
       <c r="F38" s="13" t="inlineStr"/>
       <c r="G38" s="13" t="inlineStr"/>
       <c r="H38" s="13" t="inlineStr"/>
+      <c r="I38" s="13" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
@@ -2892,11 +2871,12 @@
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr"/>
-      <c r="D39" s="13" t="inlineStr"/>
-      <c r="E39" s="14" t="inlineStr"/>
+      <c r="D39" s="14" t="inlineStr"/>
+      <c r="E39" s="13" t="inlineStr"/>
       <c r="F39" s="13" t="inlineStr"/>
       <c r="G39" s="13" t="inlineStr"/>
       <c r="H39" s="13" t="inlineStr"/>
+      <c r="I39" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -2907,13 +2887,13 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="A14:B14"/>

--- a/samples/사전과제_엑셀예시.xlsx
+++ b/samples/사전과제_엑셀예시.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>툴에서 작성자·프로세스 정보를 입력한 뒤, 시트의 [L5 활동 목록] 머리글 행부터 마지막 행까지 선택 → Ctrl+C → 툴의 활동 표 아무 칸에 Ctrl+V → 열이 맞는지 확인하고 [가져오기].</t>
+          <t>툴에서 작성자·프로세스 정보를 입력한 뒤, 시트의 [L6 활동 목록] 머리글 행부터 마지막 행까지 선택 → Ctrl+C → 툴의 활동 표 아무 칸에 Ctrl+V → 열이 맞는지 확인하고 [가져오기].</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>그 활동을 하는 사람·역할. 순서도에서 가로 레인이 됩니다. 인사팀 담당자만 적지 말고 현업·입사자·타 부서·역할도 그대로 적습니다.</t>
+          <t>그 활동을 하는 사람·역할. 순서도에서 가로 레인이 됩니다. People팀 담당자만 적지 말고 현업·입사자·타 부서·역할도 그대로 적습니다.</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -735,7 +735,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>① [과제 정보]는 툴 화면의 '작성자'와 '프로세스' 칸에 직접 입력합니다.   ② [L5 활동 목록]은 노란 머리글 행부터 마지막 행까지 범위를 선택해 복사(Ctrl+C)한 뒤, 툴 표의 아무 칸에 붙여넣습니다(Ctrl+V).</t>
+          <t>① [과제 정보]는 툴 화면의 '작성자'와 '프로세스' 칸에 직접 입력합니다.   ② [L6 활동 목록]은 노란 머리글 행부터 마지막 행까지 범위를 선택해 복사(Ctrl+C)한 뒤, 툴 표의 아무 칸에 붙여넣습니다(Ctrl+V).</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>인사팀</t>
+          <t>People팀</t>
         </is>
       </c>
       <c r="D6" s="9" t="n"/>
@@ -851,7 +851,7 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>경력 입사자 입사 처리</t>
+          <t>입사 준비</t>
         </is>
       </c>
       <c r="D11" s="9" t="n"/>
@@ -861,13 +861,13 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>E2E 시작 (트리거)</t>
+          <t>L5 주요 Task</t>
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>최종 합격자 입사 확정 (처우 협의 완료)</t>
+          <t>경력 입사자 입사 처리</t>
         </is>
       </c>
       <c r="D12" s="9" t="n"/>
@@ -877,13 +877,13 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>E2E 종료 (결과)</t>
+          <t>Process 시작 (트리거)</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>입사자 첫 출근 및 업무 환경 준비 완료</t>
+          <t>최종 합격자 입사 확정 (처우 협의 완료)</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -893,13 +893,13 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>고객</t>
+          <t>Process 종료 (결과)</t>
         </is>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>입사자, 현업 부서</t>
+          <t>입사자 첫 출근 및 업무 환경 준비 완료</t>
         </is>
       </c>
       <c r="D14" s="9" t="n"/>
@@ -909,13 +909,13 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>프로세스 오너</t>
+          <t>고객</t>
         </is>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>인사팀장</t>
+          <t>입사자, 현업 부서</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
@@ -925,105 +925,92 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>발생 빈도</t>
+          <t>프로세스 오너</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>월 10건</t>
+          <t>People팀장</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="7" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>[L5 활동 목록]  ▼ 이 아래 머리글 행부터 복사</t>
-        </is>
-      </c>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>발생 빈도</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>월 10건</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>[L6 활동 목록]  ▼ 이 아래 머리글 행부터 복사</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>유형</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>활동명</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>시스템/프로그램</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>다음 단계</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>활동</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>채용담당</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>입사 확정 통보</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>메일, 전화</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr"/>
-      <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -1032,31 +1019,27 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>입사담당</t>
+          <t>채용담당</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>입사 서류 안내</t>
+          <t>입사 확정 통보</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>메일, 전화</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr"/>
       <c r="G21" s="13" t="inlineStr"/>
       <c r="H21" s="13" t="inlineStr"/>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>제출 서류 목록을 매번 메일로 새로 작성</t>
-        </is>
-      </c>
+      <c r="I21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
@@ -1065,17 +1048,17 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>입사자</t>
+          <t>입사담당</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>입사 서류 제출</t>
+          <t>입사 서류 안내</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>메일, 종이/출력</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr"/>
@@ -1083,83 +1066,83 @@
       <c r="H22" s="13" t="inlineStr"/>
       <c r="I22" s="13" t="inlineStr">
         <is>
+          <t>제출 서류 목록을 매번 메일로 새로 작성</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>활동</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>입사자</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>입사 서류 제출</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>메일, 종이/출력</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
           <t>원본 서류는 첫 출근일에 지참</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="n">
+    <row r="24">
+      <c r="A24" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>판단</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>입사담당</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>입사 서류 보완 필요 여부 판단</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>엑셀</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr"/>
-      <c r="G23" s="16" t="inlineStr"/>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr"/>
+      <c r="G24" s="16" t="inlineStr"/>
+      <c r="H24" s="16" t="inlineStr">
         <is>
           <t>보완 필요→5, 이상 없음→6</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>누락 여부를 엑셀 체크리스트로 확인</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>활동</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>입사자</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>입사 서류 보완 제출</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>메일</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr"/>
-      <c r="G24" s="13" t="inlineStr"/>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
@@ -1168,31 +1151,31 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>입사담당</t>
+          <t>입사자</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>인사정보 등록</t>
+          <t>입사 서류 보완 제출</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>HRIS, 엑셀</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr"/>
       <c r="G25" s="13" t="inlineStr"/>
-      <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>엑셀 입사자 대장과 HRIS에 이중 입력</t>
-        </is>
-      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
@@ -1206,22 +1189,26 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>IT 계정 생성 요청</t>
+          <t>인사정보 등록</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>HRIS, 엑셀</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="13" t="inlineStr"/>
-      <c r="I26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>엑셀 입사자 대장과 HRIS에 이중 입력</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
@@ -1230,31 +1217,27 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>시스템 담당</t>
+          <t>입사담당</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>사내 계정·메일 생성</t>
+          <t>IT 계정 생성 요청</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>그룹웨어</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr"/>
       <c r="G27" s="13" t="inlineStr"/>
       <c r="H27" s="13" t="inlineStr"/>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>요청이 누락되면 첫 출근일에 계정 없음</t>
-        </is>
-      </c>
+      <c r="I27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
@@ -1263,27 +1246,31 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>입사담당</t>
+          <t>시스템 담당</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>좌석·PC 준비 요청</t>
+          <t>사내 계정·메일 생성</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>메일, 메신저</t>
+          <t>그룹웨어</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr"/>
       <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="13" t="inlineStr"/>
-      <c r="I28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>요청이 누락되면 첫 출근일에 계정 없음</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
@@ -1292,31 +1279,27 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>자산 담당</t>
+          <t>입사담당</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>좌석·PC 배정</t>
+          <t>좌석·PC 준비 요청</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>엑셀</t>
+          <t>메일, 메신저</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr"/>
       <c r="G29" s="13" t="inlineStr"/>
       <c r="H29" s="13" t="inlineStr"/>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>장비 재고를 엑셀로 관리해 확인에 1~2일 소요</t>
-        </is>
-      </c>
+      <c r="I29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
@@ -1325,17 +1308,17 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>급여담당</t>
+          <t>자산 담당</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>급여 계좌·4대보험 등록</t>
+          <t>좌석·PC 배정</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>HRIS, EDI</t>
+          <t>엑셀</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr"/>
@@ -1343,13 +1326,13 @@
       <c r="H30" s="13" t="inlineStr"/>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>4대보험 취득신고 기한(입사 후 14일) 관리 필요</t>
+          <t>장비 재고를 엑셀로 관리해 확인에 1~2일 소요</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
@@ -1358,17 +1341,17 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>팀장</t>
+          <t>급여담당</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>멘토·첫 주 업무 지정</t>
+          <t>급여 계좌·4대보험 등록</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>메일</t>
+          <t>HRIS, EDI</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr"/>
@@ -1376,13 +1359,13 @@
       <c r="H31" s="13" t="inlineStr"/>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>팀마다 준비 수준 편차가 큼</t>
+          <t>4대보험 취득신고 기한(입사 후 14일) 관리 필요</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
@@ -1391,27 +1374,31 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>입사담당</t>
+          <t>팀장</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>입사 오리엔테이션 진행</t>
+          <t>멘토·첫 주 업무 지정</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>대면, 종이/출력</t>
+          <t>메일</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr"/>
       <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="13" t="inlineStr"/>
-      <c r="I32" s="13" t="inlineStr"/>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>팀마다 준비 수준 편차가 큼</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
@@ -1420,30 +1407,60 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>입사자</t>
+          <t>입사담당</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>보안 서약서 서명</t>
+          <t>입사 오리엔테이션 진행</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>종이/출력</t>
+          <t>대면, 종이/출력</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr"/>
       <c r="G33" s="13" t="inlineStr"/>
       <c r="H33" s="13" t="inlineStr"/>
-      <c r="I33" s="13" t="inlineStr">
+      <c r="I33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>활동</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>입사자</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>보안 서약서 서명</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>종이/출력</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr"/>
+      <c r="G34" s="13" t="inlineStr"/>
+      <c r="H34" s="13" t="inlineStr"/>
+      <c r="I34" s="13" t="inlineStr">
         <is>
           <t>종이에 서명한 뒤 스캔해 보관</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="27">
+    <mergeCell ref="C17:F17"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="A11:B11"/>
@@ -1461,6 +1478,7 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C9:F9"/>
@@ -1471,7 +1489,7 @@
     <mergeCell ref="A9:B9"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B20:B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B21:B34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"활동,판단"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1485,7 +1503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1509,7 +1527,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>① [과제 정보]는 툴 화면의 '작성자'와 '프로세스' 칸에 직접 입력합니다.   ② [L5 활동 목록]은 노란 머리글 행부터 마지막 행까지 범위를 선택해 복사(Ctrl+C)한 뒤, 툴 표의 아무 칸에 붙여넣습니다(Ctrl+V).</t>
+          <t>① [과제 정보]는 툴 화면의 '작성자'와 '프로세스' 칸에 직접 입력합니다.   ② [L6 활동 목록]은 노란 머리글 행부터 마지막 행까지 범위를 선택해 복사(Ctrl+C)한 뒤, 툴 표의 아무 칸에 붙여넣습니다(Ctrl+V).</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1563,7 @@
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>인사팀</t>
+          <t>People팀</t>
         </is>
       </c>
       <c r="D6" s="9" t="n"/>
@@ -1625,7 +1643,7 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>상반기 성과평가 운영</t>
+          <t>평가 운영</t>
         </is>
       </c>
       <c r="D11" s="9" t="n"/>
@@ -1635,13 +1653,13 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>E2E 시작 (트리거)</t>
+          <t>L5 주요 Task</t>
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>평가 시즌 도래 (연간 인사 일정)</t>
+          <t>상반기 성과평가 운영</t>
         </is>
       </c>
       <c r="D12" s="9" t="n"/>
@@ -1651,13 +1669,13 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>E2E 종료 (결과)</t>
+          <t>Process 시작 (트리거)</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>평가 결과 확정 및 피드백 완료</t>
+          <t>평가 시즌 도래 (연간 인사 일정)</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -1667,13 +1685,13 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>고객</t>
+          <t>Process 종료 (결과)</t>
         </is>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>임직원, 경영진</t>
+          <t>평가 결과 확정 및 피드백 완료</t>
         </is>
       </c>
       <c r="D14" s="9" t="n"/>
@@ -1683,13 +1701,13 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>프로세스 오너</t>
+          <t>고객</t>
         </is>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>인사팀장</t>
+          <t>임직원, 경영진</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
@@ -1699,171 +1717,154 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>발생 빈도</t>
+          <t>프로세스 오너</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>연 2회</t>
+          <t>People팀장</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="7" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>[L5 활동 목록]  ▼ 이 아래 머리글 행부터 복사</t>
-        </is>
-      </c>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>발생 빈도</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>연 2회</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>[L6 활동 목록]  ▼ 이 아래 머리글 행부터 복사</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>유형</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>활동명</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>시스템/프로그램</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>다음 단계</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
+    <row r="21">
+      <c r="A21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>활동</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>활동</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>평가 일정·기준 수립</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>엑셀, 워드</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr"/>
-      <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="F21" s="13" t="inlineStr"/>
+      <c r="G21" s="13" t="inlineStr"/>
+      <c r="H21" s="13" t="inlineStr"/>
+      <c r="I21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>판단</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>인사 임원</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>평가 계획 승인 여부 판단</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>전자결재</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr"/>
-      <c r="G21" s="16" t="inlineStr"/>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr"/>
+      <c r="G22" s="16" t="inlineStr"/>
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>승인→3, 보완 요청→1</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>활동</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>평가담당</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>평가 대상자 명단 추출</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>HRIS, 엑셀</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr"/>
-      <c r="G22" s="13" t="inlineStr"/>
-      <c r="H22" s="13" t="inlineStr"/>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>휴직자·전입자는 수기로 보정</t>
-        </is>
-      </c>
+      <c r="I22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
@@ -1877,22 +1878,26 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>평가 안내 공지</t>
+          <t>평가 대상자 명단 추출</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>메일, 그룹웨어</t>
+          <t>HRIS, 엑셀</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr"/>
       <c r="G23" s="13" t="inlineStr"/>
       <c r="H23" s="13" t="inlineStr"/>
-      <c r="I23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>휴직자·전입자는 수기로 보정</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
@@ -1901,17 +1906,17 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>임직원</t>
+          <t>평가담당</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>자기평가 작성</t>
+          <t>평가 안내 공지</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>HRIS</t>
+          <t>메일, 그룹웨어</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr"/>
@@ -1921,7 +1926,7 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
@@ -1930,31 +1935,27 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>평가담당</t>
+          <t>임직원</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>미제출자 독촉</t>
+          <t>자기평가 작성</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>메일, 전화, 메신저</t>
+          <t>HRIS</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr"/>
       <c r="G25" s="13" t="inlineStr"/>
       <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>제출률을 엑셀로 집계해 개별 연락 (마감 전후 1주)</t>
-        </is>
-      </c>
+      <c r="I25" s="13" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
@@ -1963,27 +1964,31 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>1차 평가자(팀장)</t>
+          <t>평가담당</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>1차 평가 입력</t>
+          <t>미제출자 독촉</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>HRIS</t>
+          <t>메일, 전화, 메신저</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="13" t="inlineStr"/>
-      <c r="I26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>제출률을 엑셀로 집계해 개별 연락 (마감 전후 1주)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
@@ -1992,12 +1997,12 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>2차 평가자(본부장)</t>
+          <t>1차 평가자(팀장)</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>2차 평가 입력</t>
+          <t>1차 평가 입력</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -2008,15 +2013,11 @@
       <c r="F27" s="13" t="inlineStr"/>
       <c r="G27" s="13" t="inlineStr"/>
       <c r="H27" s="13" t="inlineStr"/>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>본부장 일정 때문에 지연이 잦음</t>
-        </is>
-      </c>
+      <c r="I27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
@@ -2025,17 +2026,17 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>평가담당</t>
+          <t>2차 평가자(본부장)</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>평가 등급 분포 검토</t>
+          <t>2차 평가 입력</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>HRIS, 엑셀</t>
+          <t>HRIS</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr"/>
@@ -2043,75 +2044,75 @@
       <c r="H28" s="13" t="inlineStr"/>
       <c r="I28" s="13" t="inlineStr">
         <is>
+          <t>본부장 일정 때문에 지연이 잦음</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>활동</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>평가담당</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>평가 등급 분포 검토</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>HRIS, 엑셀</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr"/>
+      <c r="G29" s="13" t="inlineStr"/>
+      <c r="H29" s="13" t="inlineStr"/>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
           <t>HRIS에서 내려받아 엑셀로 등급 비율 계산</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="15" t="n">
+    <row r="30">
+      <c r="A30" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>판단</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>등급 분포 조정 필요 여부 판단</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr"/>
-      <c r="F29" s="16" t="inlineStr"/>
-      <c r="G29" s="16" t="inlineStr"/>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr"/>
+      <c r="F30" s="16" t="inlineStr"/>
+      <c r="G30" s="16" t="inlineStr"/>
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>조정 필요→11, 이상 없음→12</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>활동</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>2차 평가자(본부장)</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>평가 등급 조정</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>HRIS, 메일</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr"/>
-      <c r="G30" s="13" t="inlineStr"/>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr"/>
+      <c r="I30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
@@ -2120,31 +2121,31 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>인사위원회</t>
+          <t>2차 평가자(본부장)</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>평가 결과 확정</t>
+          <t>평가 등급 조정</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>대면, 종이/출력</t>
+          <t>HRIS, 메일</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr"/>
       <c r="G31" s="13" t="inlineStr"/>
-      <c r="H31" s="13" t="inlineStr"/>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>회의 자료 출력물 준비에 2~3일</t>
-        </is>
-      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
@@ -2153,27 +2154,31 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>평가담당</t>
+          <t>인사위원회</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>평가 결과 통보</t>
+          <t>평가 결과 확정</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>HRIS, 메일</t>
+          <t>대면, 종이/출력</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr"/>
       <c r="G32" s="13" t="inlineStr"/>
       <c r="H32" s="13" t="inlineStr"/>
-      <c r="I32" s="13" t="inlineStr"/>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>회의 자료 출력물 준비에 2~3일</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
@@ -2182,88 +2187,118 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>팀장</t>
+          <t>평가담당</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>평가 피드백 면담</t>
+          <t>평가 결과 통보</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>대면</t>
+          <t>HRIS, 메일</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr"/>
       <c r="G33" s="13" t="inlineStr"/>
       <c r="H33" s="13" t="inlineStr"/>
-      <c r="I33" s="13" t="inlineStr">
+      <c r="I33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>활동</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>팀장</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>평가 피드백 면담</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>대면</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr"/>
+      <c r="G34" s="13" t="inlineStr"/>
+      <c r="H34" s="13" t="inlineStr"/>
+      <c r="I34" s="13" t="inlineStr">
         <is>
           <t>면담 실시 여부를 확인할 방법이 없음</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="15" t="n">
+    <row r="35">
+      <c r="A35" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>판단</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>임직원</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>이의 신청 여부 판단</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr"/>
-      <c r="F34" s="16" t="inlineStr"/>
-      <c r="G34" s="16" t="inlineStr"/>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr"/>
+      <c r="F35" s="16" t="inlineStr"/>
+      <c r="G35" s="16" t="inlineStr"/>
+      <c r="H35" s="16" t="inlineStr">
         <is>
           <t>이의 신청→16, 없음→종료</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="I35" s="16" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>활동</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>활동</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>평가담당</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>이의 신청 검토·회신</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>메일, 엑셀</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr"/>
-      <c r="G35" s="13" t="inlineStr"/>
-      <c r="H35" s="13" t="inlineStr"/>
-      <c r="I35" s="13" t="inlineStr"/>
+      <c r="F36" s="13" t="inlineStr"/>
+      <c r="G36" s="13" t="inlineStr"/>
+      <c r="H36" s="13" t="inlineStr"/>
+      <c r="I36" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="27">
+    <mergeCell ref="C17:F17"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="A11:B11"/>
@@ -2281,6 +2316,7 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C9:F9"/>
@@ -2291,7 +2327,7 @@
     <mergeCell ref="A9:B9"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B20:B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B21:B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"활동,판단"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2305,7 +2341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2329,7 +2365,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>① [과제 정보]는 툴 화면의 '작성자'와 '프로세스' 칸에 직접 입력합니다.   ② [L5 활동 목록]은 노란 머리글 행부터 마지막 행까지 범위를 선택해 복사(Ctrl+C)한 뒤, 툴 표의 아무 칸에 붙여넣습니다(Ctrl+V).</t>
+          <t>① [과제 정보]는 툴 화면의 '작성자'와 '프로세스' 칸에 직접 입력합니다.   ② [L6 활동 목록]은 노란 머리글 행부터 마지막 행까지 범위를 선택해 복사(Ctrl+C)한 뒤, 툴 표의 아무 칸에 붙여넣습니다(Ctrl+V).</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2463,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>E2E 시작 (트리거)</t>
+          <t>L5 주요 Task</t>
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
@@ -2439,7 +2475,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>E2E 종료 (결과)</t>
+          <t>Process 시작 (트리거)</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
@@ -2451,7 +2487,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>고객</t>
+          <t>Process 종료 (결과)</t>
         </is>
       </c>
       <c r="B14" s="7" t="n"/>
@@ -2463,7 +2499,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>프로세스 오너</t>
+          <t>고객</t>
         </is>
       </c>
       <c r="B15" s="7" t="n"/>
@@ -2475,7 +2511,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>발생 빈도</t>
+          <t>프로세스 오너</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -2484,80 +2520,75 @@
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="7" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>[L5 활동 목록]  ▼ 이 아래 머리글 행부터 복사</t>
-        </is>
-      </c>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>발생 빈도</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>[L6 활동 목록]  ▼ 이 아래 머리글 행부터 복사</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>유형</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>활동명</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>시스템/프로그램</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>다음 단계</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>활동</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="13" t="inlineStr"/>
-      <c r="F20" s="13" t="inlineStr"/>
-      <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -2574,7 +2605,7 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
@@ -2591,7 +2622,7 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
@@ -2608,7 +2639,7 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
@@ -2625,7 +2656,7 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
@@ -2642,7 +2673,7 @@
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
@@ -2659,7 +2690,7 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
@@ -2676,7 +2707,7 @@
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
@@ -2693,7 +2724,7 @@
     </row>
     <row r="29">
       <c r="A29" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
@@ -2710,7 +2741,7 @@
     </row>
     <row r="30">
       <c r="A30" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
@@ -2727,7 +2758,7 @@
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
@@ -2744,7 +2775,7 @@
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
@@ -2761,7 +2792,7 @@
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
@@ -2778,7 +2809,7 @@
     </row>
     <row r="34">
       <c r="A34" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
@@ -2795,7 +2826,7 @@
     </row>
     <row r="35">
       <c r="A35" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
@@ -2812,7 +2843,7 @@
     </row>
     <row r="36">
       <c r="A36" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
@@ -2829,7 +2860,7 @@
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
@@ -2846,7 +2877,7 @@
     </row>
     <row r="38">
       <c r="A38" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
@@ -2863,7 +2894,7 @@
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
@@ -2878,8 +2909,26 @@
       <c r="H39" s="13" t="inlineStr"/>
       <c r="I39" s="13" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>활동</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr"/>
+      <c r="D40" s="14" t="inlineStr"/>
+      <c r="E40" s="13" t="inlineStr"/>
+      <c r="F40" s="13" t="inlineStr"/>
+      <c r="G40" s="13" t="inlineStr"/>
+      <c r="H40" s="13" t="inlineStr"/>
+      <c r="I40" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="27">
+    <mergeCell ref="C17:F17"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="A11:B11"/>
@@ -2897,6 +2946,7 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C9:F9"/>
@@ -2907,7 +2957,7 @@
     <mergeCell ref="A9:B9"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B20:B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B21:B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"활동,판단"</formula1>
     </dataValidation>
   </dataValidations>
